--- a/Result/checksun_type/有線通訊設備(如電話機、傳真機).xlsx
+++ b/Result/checksun_type/有線通訊設備(如電話機、傳真機).xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>72.5</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>72.56</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>76.49</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>72.56</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>76.48999999999999</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>13865.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>6521.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>6521</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>6483.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>21480.66</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>21480.66</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-418.6888189420579</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>13865</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>13865.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>71.88</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>72.56</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>76.7</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>72.56</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>76.7</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>2571.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4450.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>4450.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>5653.3</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>25516.7</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>25516.7</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-1216.68766164667</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>2571</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2571.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>71.34</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>72.65</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>76.88</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>72.65000000000001</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>76.88</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>3855.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>6143.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>6143.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>5750.2</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>26372.9</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>26372.9</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1103.16144902302</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>3855</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>3855.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>71.36</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>72.83</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>76.93</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>72.83</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>76.93000000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>9753.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>6941.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>6941.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>5791.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>26625.5</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>26625.5</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-1039.153950666985</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>9753</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>9753.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>71.46000000000001</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>73.18</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>77.05</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>77.05</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>2561.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>5857.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>5857.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>5323.1</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>26894.5</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>26894.5</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-1542.530597634543</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>2561</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>2561.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>71.72</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>73.57</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>77.13</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>73.56999999999999</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>77.13</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>3514.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>6445.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>6445.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>5397.3</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>27392.76</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>27392.76</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-1435.978286244104</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>3514</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3514.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>72.03999999999999</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>73.92</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>77.15</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>73.92</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>77.15000000000001</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>11034.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>6855.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>6855.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>5439.7</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>27408.92</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>27408.92</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-1334.582902606189</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>11034</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>11034.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>72.38000000000001</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>74.24</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>77.17</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>74.23999999999999</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>77.17</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>7847.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>5357.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>5357</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>4769.0</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>27235.36</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>27235.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-1947.782965173234</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>7847</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>7847.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>72.32000000000001</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>74.34</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>77.13</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>74.34</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>77.13</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>4331.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>4641.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>4641.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>4327.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>27108.7</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>27108.7</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-2412.755091512823</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>4331</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>4331.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>72.56</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>74.52</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>77.12</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>74.52</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>77.12</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>5502.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>4788.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>4788.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>5092.8</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>27277.66</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>27277.66</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-2614.116875872493</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>5502</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>5502.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>72.64000000000001</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>74.7</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>77.11</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>77.11</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>5565.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>4349.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>4349</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>5652.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>27276.18</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>27276.18</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-2933.879536533719</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>5565</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>5565.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5667,11 +5601,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>8034</t>
@@ -5853,41 +5783,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr">
         <is>
           <t>0</t>
@@ -5908,20 +5834,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>0</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5860,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>0</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6029,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6213,11 @@
           <t>42.55</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>42.6</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>41.46</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>41.46</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6264,16 @@
           <t>2767.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>3043.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>3043.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>10093.3</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>5362.4</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>5362.4</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6290,10 @@
           <t>-1010.262975570905</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>2767</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>2767.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6459,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6643,11 @@
           <t>42.73999999999999</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>41.42</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>41.42</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6694,16 @@
           <t>2040.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>3751.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>3751.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>10263.0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>5439.54</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>5439.54</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6720,10 @@
           <t>-806.2180643579304</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>2040</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6889,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7073,11 @@
           <t>43.22</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>42.4</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>41.4</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>41.4</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7124,16 @@
           <t>2843.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>7527.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>7527</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>10587.5</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>5531.16</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>5531.16</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7150,10 @@
           <t>-408.0389746123274</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>2843</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>2843.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7319,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7503,11 @@
           <t>43.68</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>42.32</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>41.38</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>42.32</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>41.38</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7554,16 @@
           <t>4645.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>8850.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>8850</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>11384.5</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>5680.18</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>5680.18</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7580,10 @@
           <t>89.32540268897355</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>4645</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>4645.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7749,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7933,11 @@
           <t>44.29</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>42.22</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>42.22</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>41.37</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7984,16 @@
           <t>2921.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>10771.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>10771.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>13133.0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>5760.5</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>5760.5</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8010,10 @@
           <t>603.5843201662283</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>2921</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>2921.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8179,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8363,11 @@
           <t>44.69</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>41.33</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>41.33</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8414,16 @@
           <t>6307.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>17143.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>17143.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>13297.5</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>5823.24</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>5823.24</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8440,10 @@
           <t>1501.397619413508</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>6307</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>6307.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8609,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8793,11 @@
           <t>44.52</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>41.94</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>41.3</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>41.94</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>41.3</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8844,16 @@
           <t>20919.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>16774.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>16774.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>13033.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>5739.88</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>5739.88</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8870,10 @@
           <t>2367.580989073429</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>20919</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>20919.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9039,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9223,11 @@
           <t>44.02</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>41.77</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>41.24</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>41.77</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>41.24</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9274,16 @@
           <t>9458.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>13648.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>13648</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>11284.3</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>5386.6</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>5386.6</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9300,10 @@
           <t>1954.857910406408</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>9458</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>9458.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9469,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9653,11 @@
           <t>43.55</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>41.6</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>41.18</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>41.18</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9704,16 @@
           <t>14252.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>13919.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>13919</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>10532.3</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>5296.48</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>5296.48</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9730,10 @@
           <t>2523.401444081863</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>14252</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>14252.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9899,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10083,11 @@
           <t>43.07</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>41.36</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>41.12</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>41.12</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10134,16 @@
           <t>34781.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>15494.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>15494.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>9420.7</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>5066.56</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>5066.56</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10160,10 @@
           <t>2731.842154901018</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>34781</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>34781.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10329,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10513,11 @@
           <t>42.25000000000001</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>41.06</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>41.06</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>41.06</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10564,16 @@
           <t>4464.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>9451.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>9451.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>6642.1</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>4486.98</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>4486.98</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10590,10 @@
           <t>732.5130933962018</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>4464</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>4464.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10759,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10943,11 @@
           <t>127.1</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>129.52</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>135.77</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>129.52</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>135.77</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10994,16 @@
           <t>5885.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>4913.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>4913.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>9574.5</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>9511.3</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>9511.299999999999</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11020,10 @@
           <t>-859.9149679335142</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>5885</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>5885.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11189,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11373,11 @@
           <t>126.4</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>129.72</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>136.17</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>129.72</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>136.17</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11424,16 @@
           <t>4210.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>6538.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>6538</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>9700.7</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>9957.02</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>9957.02</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11450,10 @@
           <t>-851.4500188526199</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>4210</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>4210.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11619,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11803,11 @@
           <t>126.4</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>130.02</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>136.62</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>130.02</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>136.62</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11854,16 @@
           <t>2218.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>8348.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>8348.799999999999</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>9820.2</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>10311.8</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>10311.8</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11880,10 @@
           <t>-629.4840194923199</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>2218</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>2218.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12049,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12233,11 @@
           <t>127.0</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>130.3</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>137.03</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>130.3</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>137.03</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12284,16 @@
           <t>6198.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>9740.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>9740.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>11050.1</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>10746.7</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>10746.7</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12310,10 @@
           <t>-76.47959113859542</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>6198</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>6198.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12479,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12663,11 @@
           <t>128.3</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>130.7</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>137.37</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>137.37</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12714,16 @@
           <t>6055.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>11431.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>11431.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>11045.3</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>10673.4</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>10673.4</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12740,10 @@
           <t>289.8295776216764</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>6055</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>6055.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12909,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13093,11 @@
           <t>129.1</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>131.1</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>137.69</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>131.1</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>137.69</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13144,16 @@
           <t>14009.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>14235.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>14235.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>10887.4</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>10665.32</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>10665.32</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13170,10 @@
           <t>818.0987623641486</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>14009</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>14009.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13339,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13523,11 @@
           <t>130.1</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>138.02</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>138.02</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13574,16 @@
           <t>13264.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>12863.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>12863.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>10152.5</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>10437.88</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>10437.88</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13600,10 @@
           <t>691.3369276261019</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>13264</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>13264.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13769,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13953,11 @@
           <t>130.7</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>131.72</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>138.32</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>131.72</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>138.32</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14004,16 @@
           <t>9177.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>11291.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>11291.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>9761.8</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>10259.3</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>10259.3</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14030,10 @@
           <t>565.3794162993872</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>9177</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>9177.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14199,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14383,11 @@
           <t>130.8</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>131.93</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>138.57</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>131.93</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>138.57</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14434,16 @@
           <t>14654.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>12359.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>12359.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>9213.8</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>10181.52</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>10181.52</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14460,10 @@
           <t>803.1408495362484</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>14654</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>14654.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14629,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14813,11 @@
           <t>130.3</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>131.98</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>138.77</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>131.98</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>138.77</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14864,16 @@
           <t>20075.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>10658.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>10658.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>8431.7</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>10026.46</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>10026.46</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14890,10 @@
           <t>527.295009534042</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>20075</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>20075.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15059,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15243,11 @@
           <t>130.3</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>132.15</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>139.03</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>132.15</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>139.03</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15294,16 @@
           <t>7147.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>7539.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>7539</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>6953.4</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>9713.12</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>9713.120000000001</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15320,10 @@
           <t>-466.4238693810394</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>7147</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>7147.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15489,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15673,11 @@
           <t>28.26</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>29.26</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>31.21</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>29.26</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>31.21</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15724,16 @@
           <t>5336.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>10611.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>10611</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>10115.7</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>18347.6</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>18347.6</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15750,10 @@
           <t>-1270.022160241968</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>5336</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>5336.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15919,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16103,11 @@
           <t>27.86</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>29.36</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>31.35</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>31.35</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16154,16 @@
           <t>6570.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>11270.8</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>11270.8</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>10715.7</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>19506.8</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>19506.8</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16180,10 @@
           <t>-973.009376675931</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>6570</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>6570.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16349,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16533,11 @@
           <t>27.71</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>31.54</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>31.54</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16584,16 @@
           <t>5117.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>12767.0</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>12767</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>11052.2</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>22495.74</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>22495.74</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16610,10 @@
           <t>-646.1693509860233</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>5117</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>5117.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16779,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16963,11 @@
           <t>28.0</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>29.69</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>31.73</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>29.69</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>31.73</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17014,16 @@
           <t>25968.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>13339.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>13339.4</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>11487.5</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>23094.84</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>23094.84</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17040,10 @@
           <t>-0.4989803223670606</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>25968</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>25968.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17209,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17393,11 @@
           <t>28.42000000000001</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>29.91</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>31.93</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>29.91</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>31.93</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17444,16 @@
           <t>10064.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>10402.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>10402</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>10840.2</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>23019.14</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>23019.14</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17470,10 @@
           <t>-1312.130630077061</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>10064</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>10064.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17639,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17823,11 @@
           <t>28.8</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>30.1</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>32.12</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>32.12</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17874,16 @@
           <t>8635.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>9620.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>9620.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>10491.6</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>23199.26</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>23199.26</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17900,10 @@
           <t>-1435.028321509588</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>8635</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>8635.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18069,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18253,11 @@
           <t>29.36</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>30.34</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>32.34</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>32.34</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18304,16 @@
           <t>14051.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>10160.6</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>10160.6</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>11338.5</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>23447.42</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>23447.42</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18330,10 @@
           <t>-1406.238297787853</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>14051</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>14051.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18499,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18683,11 @@
           <t>29.72</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>30.55</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>32.55</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>32.55</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18734,16 @@
           <t>7979.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>9337.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>9337.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>10907.2</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>23467.6</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>23467.6</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18760,10 @@
           <t>-1895.172610407239</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>7979</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>7979.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18929,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19113,11 @@
           <t>29.79</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>32.72</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>32.72</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19164,16 @@
           <t>11281.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>9635.6</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>9635.6</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>10939.5</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>23804.18</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>23804.18</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19190,10 @@
           <t>-1875.3940352061</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>11281</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>11281.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19359,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19543,11 @@
           <t>29.75</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>30.82</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>32.9</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>30.82</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>32.9</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19594,16 @@
           <t>6156.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>11278.4</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>11278.4</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>11278.7</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>24780.32</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>24780.32</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19620,10 @@
           <t>-2133.946283661398</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>6156</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>6156.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19789,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19973,11 @@
           <t>29.76</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>30.92</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>33.13</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>30.92</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>33.13</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20024,16 @@
           <t>11336.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>11362.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>11362.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>12413.1</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>25613.64</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>25613.64</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20050,10 @@
           <t>-1877.987128466777</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>11336</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>11336.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20219,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20403,11 @@
           <t>24.2</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>24.54</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>25.41</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>25.41</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20454,16 @@
           <t>494.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>1144.2</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>1144.2</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>937.5</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>1006.5</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>1006.5</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20480,10 @@
           <t>38.85005539776387</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>494</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>494.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20649,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20833,11 @@
           <t>24.13</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>24.59</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>24.59</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>25.43</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20884,16 @@
           <t>2191.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>1244.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>1244</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>1009.3</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>1040.24</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>1040.24</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20910,10 @@
           <t>101.7666215778704</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>2191</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>2191.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21079,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21263,11 @@
           <t>24.12</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>25.45</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21314,16 @@
           <t>1003.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>951.2</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>951.2</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>904.8</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>1020.52</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>1020.52</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21340,10 @@
           <t>6.19147963595583</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>1003</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>1003.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21509,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21693,11 @@
           <t>24.31</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>24.72</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>25.48</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>25.48</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21744,16 @@
           <t>617.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>901.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>901.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>885.2</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>1015.8</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>1015.8</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21770,10 @@
           <t>-3.279847410920638</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>617</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>617.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21939,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22123,11 @@
           <t>24.46</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>24.79</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>25.51</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>25.51</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22174,16 @@
           <t>1416.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>861.0</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>861</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>874.8</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>1023.4</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>1023.4</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22200,10 @@
           <t>24.66396564393176</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>1416</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>1416.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22369,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22553,11 @@
           <t>24.53</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>24.84</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>25.54</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>25.54</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22604,16 @@
           <t>993.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>730.8</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>730.8</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>789.9</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>1007.34</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>1007.34</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22630,10 @@
           <t>-21.90430019356234</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>993</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>993.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22799,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22983,11 @@
           <t>24.63</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>24.91</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>25.57</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>24.91</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>25.57</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23034,16 @@
           <t>727.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>774.6</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>774.6</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>814.0</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>995.16</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>995.16</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23060,10 @@
           <t>-42.32666924021248</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>727</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>727.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23229,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,21 +23413,17 @@
           <t>24.64</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>24.98</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
+      <c r="AM54" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="AO54" t="inlineStr">
         <is>
           <t>25.59</t>
         </is>
       </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>25.59</t>
-        </is>
-      </c>
       <c r="AP54" t="inlineStr">
         <is>
           <t>5.08</t>
@@ -23784,20 +23464,16 @@
           <t>754.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>858.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>858.4</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>880.3</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>998.32</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>998.3200000000001</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23490,10 @@
           <t>-41.48981540541934</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>754</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>754.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23659,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,21 +23843,17 @@
           <t>24.52</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>25.01</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
+      <c r="AM55" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AO55" t="inlineStr">
         <is>
           <t>25.6</t>
         </is>
       </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>25.6</t>
-        </is>
-      </c>
       <c r="AP55" t="inlineStr">
         <is>
           <t>-3.50</t>
@@ -24220,20 +23894,16 @@
           <t>415.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>869.0</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>869</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>873.6</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>990.12</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>990.12</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23920,10 @@
           <t>-41.70538794837853</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>415</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>415.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24089,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24273,11 @@
           <t>24.46</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>25.62</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>25.62</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24324,16 @@
           <t>765.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>888.6</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>888.6</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>898.3</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>993.48</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>993.48</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24350,10 @@
           <t>-4.202442011592325</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>765</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>765.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24519,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24703,11 @@
           <t>24.42</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>25.09</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>25.63</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>25.09</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>25.63</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24754,16 @@
           <t>1212.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>849.0</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>849</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>927.4</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>1004.44</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>1004.44</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24780,10 @@
           <t>12.02328225565896</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>1212</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>1212.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24949,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25133,11 @@
           <t>34.45999999999999</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>35.14</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>34.83</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>35.14</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>34.83</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25184,16 @@
           <t>444179356.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>136269644.2</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>136269644.2</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>122088272.4</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>163830768.38</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>163830768.38</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25210,10 @@
           <t>7128213.503416479</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>444179356</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>444179356.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25379,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25563,11 @@
           <t>33.79000000000001</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>35.1</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>34.83</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>34.83</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25614,16 @@
           <t>66242265.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>62797967.6</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>62797967.6</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>92285347.9</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>168909276.52</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>168909276.52</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25640,10 @@
           <t>-22420787.21214063</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>66242265</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>66242265.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25809,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25993,11 @@
           <t>33.64</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>35.08</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>34.9</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>35.08</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>34.9</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26044,16 @@
           <t>60800377.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>71492279.0</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>71492279</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>109737098.5</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>176011588.5</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>176011588.5</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26070,10 @@
           <t>-23339643.22678861</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>60800377</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>60800377.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26239,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26423,11 @@
           <t>33.98</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>35.16</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>35.02</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>35.16</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>35.02</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26474,16 @@
           <t>58295854.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>76956669.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>76956669.40000001</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>114437601.6</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>200903568.92</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>200903568.92</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26500,10 @@
           <t>-23235676.56104328</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>58295854</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>58295854.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26669,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26853,11 @@
           <t>34.47000000000001</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>35.25</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>35.12</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>35.12</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26904,16 @@
           <t>51830369.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>90408769.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>90408769.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>118829125.7</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>212619498.64</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>212619498.64</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26930,10 @@
           <t>-21988965.41136982</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>51830369</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>51830369.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27099,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27283,11 @@
           <t>34.82000000000001</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>35.28</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>35.17</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>35.17</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27334,16 @@
           <t>76820973.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>107906900.6</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>107906900.6</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>132363323.5</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>233115481.42</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>233115481.42</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27360,10 @@
           <t>-18729898.75428739</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>76820973</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>76820973.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27529,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27713,11 @@
           <t>35.21</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>35.35</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>35.22</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>35.35</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>35.22</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27764,16 @@
           <t>109713822.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>121772728.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>121772728.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>144970121.5</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>260507448.8</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>260507448.8</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27790,10 @@
           <t>-16082729.00294507</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>109713822</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>109713822.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27959,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28143,11 @@
           <t>35.33</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>35.42</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>35.19</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>35.42</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>35.19</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28194,16 @@
           <t>88122329.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>147981918.0</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>147981918</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>147647629.9</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>265222232.22</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>265222232.22</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28220,10 @@
           <t>-15250908.57235089</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>88122329</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>88122329.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28389,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28573,11 @@
           <t>35.5</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>35.44</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>35.07</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>35.07</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28624,16 @@
           <t>125556356.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>151918533.8</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>151918533.8</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>154205796.2</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>266869976.8</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>266869976.8</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28650,10 @@
           <t>-11204544.1153467</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>125556356</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>125556356.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28819,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29003,11 @@
           <t>35.69</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>35.3</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>34.98</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>34.98</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29054,16 @@
           <t>139321023.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>147249481.6</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>147249481.6</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>155544218.1</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>276807183.58</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>276807183.58</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29080,10 @@
           <t>-9034649.779792577</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>139321023</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>139321023.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29249,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29433,11 @@
           <t>35.68</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>35.09</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>34.94</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>35.09</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>34.94</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29484,16 @@
           <t>146150111.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>156819746.4</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>156819746.4</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>204062083.6</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>284844626.6</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>284844626.6</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29510,10 @@
           <t>-7086920.415436953</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>146150111</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>146150111.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29679,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29863,11 @@
           <t>130.2</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>137.43</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>148.32</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>137.43</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>148.32</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29914,16 @@
           <t>20570.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>17470.4</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>17470.4</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>24111.4</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>51683.96</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>51683.96</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29940,10 @@
           <t>-4973.433186875209</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>20570</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>20570.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30109,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30293,11 @@
           <t>129.0</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>138.43</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>148.91</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>138.43</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>148.91</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30344,16 @@
           <t>13803.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>19673.8</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>19673.8</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>25953.5</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>53070.64</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>53070.64</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30370,10 @@
           <t>-5390.586435160327</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>13803</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>13803.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30539,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30723,11 @@
           <t>129.4</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>139.4</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>149.59</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>139.4</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>149.59</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30774,16 @@
           <t>13692.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>21514.0</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>21514</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>28469.8</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>53802.78</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>53802.78</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30800,10 @@
           <t>-5068.962988597632</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>13692</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>13692.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30969,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31153,11 @@
           <t>129.8</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>140.55</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>150.28</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>140.55</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>150.28</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31204,16 @@
           <t>20413.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>24577.0</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>24577</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>31279.1</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>55398.44</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>55398.44</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31230,10 @@
           <t>-4416.573672486724</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>20413</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>20413.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31399,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31583,11 @@
           <t>130.6</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>141.57</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>151.0</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>151</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31634,16 @@
           <t>18874.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>27013.6</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>27013.6</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>36177.5</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>55868.1</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>55868.1</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31660,10 @@
           <t>-4046.961304025182</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>18874</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>18874.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31829,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32013,11 @@
           <t>132.1</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>142.7</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>151.66</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>142.7</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>151.66</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32064,16 @@
           <t>31587.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>30752.4</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>30752.4</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>40368.6</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>56496.58</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>56496.58</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32090,10 @@
           <t>-3209.516445364934</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>31587</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>31587.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32259,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32443,11 @@
           <t>134.3</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>152.39</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>144</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>152.39</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32494,16 @@
           <t>23004.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>32233.2</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>32233.2</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>44188.9</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>57612.94</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>57612.94</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32520,10 @@
           <t>-3260.648202801553</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>23004</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>23004.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32689,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32873,11 @@
           <t>134.8</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>144.9</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>153.04</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>153.04</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32924,16 @@
           <t>29007.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>35425.6</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>35425.6</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>47699.4</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>58127.3</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>58127.3</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32950,10 @@
           <t>-2297.634706182376</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>29007</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>29007.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33119,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33303,11 @@
           <t>135.2</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>145.88</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>153.76</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>145.88</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>153.76</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33354,16 @@
           <t>32596.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>37981.2</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>37981.2</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>47208.4</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>61196.22</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>61196.22</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33380,10 @@
           <t>-1483.021328648465</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>32596</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>32596.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33549,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33733,11 @@
           <t>136.2</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>146.8</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>154.41</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>146.8</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>154.41</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33784,16 @@
           <t>37568.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>45341.4</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>45341.4</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>48606.6</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>63101.18</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>63101.18</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33810,10 @@
           <t>-650.8585990054344</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>37568</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>37568.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33979,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34163,11 @@
           <t>137.1</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>147.32</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>155.11</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>147.32</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>155.11</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34214,16 @@
           <t>38991.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>49984.8</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>49984.8</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>50134.0</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>64645.72</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>64645.72</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34240,10 @@
           <t>28.47596473480371</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>38991</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>38991.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34409,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34593,11 @@
           <t>19.25</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>19.74</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>20.13</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34644,16 @@
           <t>3847834.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>1895258.4</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>1895258.4</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>1471399.6</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>2167598.64</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>2167598.64</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34670,10 @@
           <t>128725.1200794668</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>3847834</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>3847834.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34839,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35023,11 @@
           <t>19.25</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>20.13</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35074,16 @@
           <t>1233198.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>1369663.6</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>1369663.6</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>1363475.2</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>2148522.86</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>2148522.86</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35100,10 @@
           <t>-64816.37283714046</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>1233198</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>1233198.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35269,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35453,11 @@
           <t>19.31</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>19.86</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35504,16 @@
           <t>1932137.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>1292743.0</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>1292743</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>1286115.6</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>2147117.6</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>2147117.6</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35530,10 @@
           <t>-58849.77797382418</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>1932137</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>1932137.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35699,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35883,11 @@
           <t>19.43</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>19.92</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35934,16 @@
           <t>1146463.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>1259223.2</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>1259223.2</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>1347515.8</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>2123313.92</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>2123313.92</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35960,10 @@
           <t>-123110.6146700217</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>1146463</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>1146463.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36129,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36313,11 @@
           <t>19.51</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>19.96</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36364,16 @@
           <t>1316660.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>1103917.0</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>1103917</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>1374269.5</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>2138601.12</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>2138601.12</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36390,10 @@
           <t>-126335.6451406602</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>1316660</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>1316660.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36559,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36743,11 @@
           <t>19.62</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36794,16 @@
           <t>1219860.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>1047540.8</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>1047540.8</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>1310455.5</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>2150367.64</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>2150367.64</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36820,10 @@
           <t>-144666.2370579774</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>1219860</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>1219860.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36989,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37173,11 @@
           <t>19.78</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>20.04</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>20.15</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>20.15</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37224,16 @@
           <t>848595.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>1357286.8</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>1357286.8</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>1330086.2</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>2135168.2</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>2135168.2</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37250,10 @@
           <t>-155314.7170449309</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>848595</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>848595.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37419,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37603,11 @@
           <t>19.85</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>20.08</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>20.16</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>20.16</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37654,16 @@
           <t>1764538.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>1279488.2</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>1279488.2</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>1676457.5</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>2144303.58</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>2144303.58</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37680,10 @@
           <t>-125201.4842746884</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>1764538</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>1764538.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37849,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38033,11 @@
           <t>19.84</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>20.09</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>20.15</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>20.15</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38084,16 @@
           <t>369932.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>1435808.4</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>1435808.4</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>1636380.0</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>2147606.34</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>2147606.34</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38110,10 @@
           <t>-175847.8487359602</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>369932</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>369932.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38279,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38463,11 @@
           <t>19.86</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38514,16 @@
           <t>1034779.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>1644622.0</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>1644622</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>1680797.2</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>2162187.9</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>2162187.9</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38540,10 @@
           <t>-92497.44622577867</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>1034779</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>1034779.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38709,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38893,11 @@
           <t>19.86</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38944,16 @@
           <t>2768590.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>1573370.2</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>1573370.2</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>1650880.1</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>2155087.0</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>2155087</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38970,10 @@
           <t>-41355.5695603129</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>2768590</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>2768590.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39139,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39323,11 @@
           <t>32.36</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>33.57</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>36.62</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>36.62</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39374,16 @@
           <t>403535423.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>568945866.2</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>568945866.2</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>551325175.1</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>652100733.04</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>652100733.04</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39400,10 @@
           <t>-64629376.5640012</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>403535423</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>403535423.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39569,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39753,11 @@
           <t>32.41</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>33.75</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>36.78</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>36.78</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39804,16 @@
           <t>363440217.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>575528949.6</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>575528949.6</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>594264436.4</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>657290966.96</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>657290966.96</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39830,10 @@
           <t>-58722927.5542357</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>363440217</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>363440217.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +39999,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40183,11 @@
           <t>32.3</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>33.94</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>36.93</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>36.93</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40234,16 @@
           <t>451484020.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>575978704.8</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>575978704.8</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>641378457.8</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>656768454.26</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>656768454.26</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40260,10 @@
           <t>-43891980.91334808</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>451484020</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>451484020.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40429,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40613,11 @@
           <t>32.09</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>34.14</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>37.07</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>37.07</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40664,16 @@
           <t>569640781.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>620997783.6</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>620997783.6</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>705807978.8</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>655783883.94</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>655783883.9400001</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40690,10 @@
           <t>-30570608.14374614</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>569640781</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>569640781.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40859,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41043,11 @@
           <t>32.14</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>34.4</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>37.2</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41094,16 @@
           <t>1056628890.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>631631786.8</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>631631786.8</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>709807982.0</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>651233510.34</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>651233510.34</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41120,10 @@
           <t>-23107921.14632392</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>1056628890</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>1056628890.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41289,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41473,11 @@
           <t>32.12</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>34.62</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>37.31</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>37.31</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41524,16 @@
           <t>436450840.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>533704484.0</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>533704484</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>667262298.9</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>638216857.76</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>638216857.76</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41550,10 @@
           <t>-63798954.21620893</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>436450840</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>436450840.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41719,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41903,11 @@
           <t>32.35</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>37.46</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>37.46</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41954,16 @@
           <t>365688993.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>612999923.2</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>612999923.2</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>705359369.1</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>635887126.76</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>635887126.76</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41980,10 @@
           <t>-53202819.16546595</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>365688993</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>365688993.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42149,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42333,11 @@
           <t>32.81</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>35.28</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>37.61</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>37.61</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42384,16 @@
           <t>676579414.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>706778210.8</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>706778210.8</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>768838281.6</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>633235828.68</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>633235828.6799999</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42410,10 @@
           <t>-28583756.22992349</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>676579414</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>676579414.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42579,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42763,11 @@
           <t>33.39</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>35.56</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>37.76</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>37.76</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42814,16 @@
           <t>622810797.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>790618174.0</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>790618174</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>763691422.1</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>627286041.56</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>627286041.5599999</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42840,10 @@
           <t>-25702505.84950864</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>622810797</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>622810797.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43009,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43193,11 @@
           <t>34.07</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>35.84</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>37.9</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43244,16 @@
           <t>566992376.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>787984177.2</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>787984177.2</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>817890552.4</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>622376486.36</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>622376486.36</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43270,10 @@
           <t>-14907563.99000478</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>566992376</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>566992376.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43439,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43623,11 @@
           <t>34.47</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>38.03</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>38.03</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43674,16 @@
           <t>832928036.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>800820113.8</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>800820113.8</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>848956198.4</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>625070436.22</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>625070436.22</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43700,10 @@
           <t>7026739.630357981</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>832928036</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>832928036.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43869,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44053,11 @@
           <t>17.21</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>17.67</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>17.7</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>17.7</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44104,16 @@
           <t>12502.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>63686.6</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>63686.6</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>0</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44130,10 @@
           <t>-22386.95193747136</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>12502</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>12502.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44299,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44483,11 @@
           <t>17.11</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>17.71</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>17.71</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>17.71</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44534,16 @@
           <t>166308.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>108736.2</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>108736.2</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>0</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44560,10 @@
           <t>-15419.1611108529</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>166308</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>166308.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44729,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44913,11 @@
           <t>17.11</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>17.74</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>17.74</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>17.74</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44964,16 @@
           <t>71451.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>0</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>0</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44990,10 @@
           <t>-21393.70417601036</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>71451</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>71451.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45159,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45343,11 @@
           <t>17.24</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>17.86</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>17.8</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45394,16 @@
           <t>4453.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>0</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>0</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45420,10 @@
           <t>-19001.45483423493</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>4453</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>4453.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45589,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45773,11 @@
           <t>17.32</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>17.95</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>17.86</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>17.86</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45824,16 @@
           <t>63719.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>0</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>0</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45850,10 @@
           <t>-7726.975244761648</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>63719</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>63719.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46019,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46203,11 @@
           <t>17.54</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>17.98</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>17.92</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>17.92</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46254,16 @@
           <t>237750.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>0</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>0</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46280,10 @@
           <t>2305.458998941671</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>237750</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>237750.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46449,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46633,11 @@
           <t>17.64</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>18.05</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>17.97</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>17.97</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46684,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>0</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>0</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46710,10 @@
           <t>-3900.529945894959</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>0</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46879,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47063,11 @@
           <t>17.74</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>18.08</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>18.01</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>18.01</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47114,16 @@
           <t>1191.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>170113.2</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>170113.2</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>159085.8</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>274061.22</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>274061.22</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47140,10 @@
           <t>-3900.529945894959</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>1191</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>1191.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47309,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47493,11 @@
           <t>17.87</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>18.06</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>18.06</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47544,16 @@
           <t>410847.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>292157.8</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>292157.8</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>159046.9</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>277939.12</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>277939.12</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47570,10 @@
           <t>14685.22151232968</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>410847</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>410847.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47739,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47923,11 @@
           <t>18.0</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>18.1</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47974,16 @@
           <t>214744.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>213319.2</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>213319.2</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>138516.7</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>303773.78</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>303773.78</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48000,10 @@
           <t>-3179.891458504018</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>214744</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>214744.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48169,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48353,11 @@
           <t>17.99</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>18.06</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>18.12</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>18.12</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48404,16 @@
           <t>128695.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>176324.0</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>176324</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>140812.3</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>316284.36</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>316284.36</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48430,10 @@
           <t>-7576.878150462784</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>128695</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>128695.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48599,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48783,11 @@
           <t>34.14</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>34.28</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>35.67</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>34.28</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>35.67</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48834,16 @@
           <t>703729.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>832338.4</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>832338.4</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>1365486.3</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>2770195.72</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>2770195.72</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48860,10 @@
           <t>-407242.1677682393</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>703729</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>703729.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49029,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49213,11 @@
           <t>34.05</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>34.34</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>35.73</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>35.73</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49264,16 @@
           <t>811272.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>1025107.0</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>1025107</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>1422951.5</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>2781982.36</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>2781982.36</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49290,10 @@
           <t>-397836.2898797004</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>811272</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>811272.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49459,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49643,11 @@
           <t>33.98</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>34.42</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>35.78</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>34.42</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>35.78</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49694,16 @@
           <t>1487179.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>1339575.6</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>1339575.6</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>1890505.4</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>2785701.92</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>2785701.92</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49720,10 @@
           <t>-381713.3468289413</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>1487179</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>1487179.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49889,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50073,11 @@
           <t>33.97</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>34.5</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>35.84</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>35.84</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50124,16 @@
           <t>582054.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>1655590.0</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>1655590</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>2092838.2</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>2769787.1</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>2769787.1</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50150,10 @@
           <t>-417466.5586553942</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>582054</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>582054.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50319,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50503,11 @@
           <t>33.92999999999999</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>34.57</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>35.9</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>34.57</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>35.9</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50554,16 @@
           <t>577458.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>1688519.2</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>1688519.2</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>2334206.6</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>2765629.48</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>2765629.48</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50580,10 @@
           <t>-356655.3770269202</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>577458</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>577458.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50749,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50933,11 @@
           <t>33.93</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>34.66</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>35.97</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>35.97</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50984,16 @@
           <t>1667572.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>1898634.2</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>1898634.2</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>2466923.8</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>2771121.32</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>2771121.32</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51010,10 @@
           <t>-256552.1398067102</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>1667572</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>1667572.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51179,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51363,11 @@
           <t>33.97</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>34.74</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>36.03</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>34.74</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>36.03</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51414,16 @@
           <t>2383615.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>1820796.0</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>1820796</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>2506266.8</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>2754839.88</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>2754839.88</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51440,10 @@
           <t>-221182.8673561704</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>2383615</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>2383615.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51609,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51793,11 @@
           <t>33.98999999999999</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>34.83</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>36.09</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51844,16 @@
           <t>3067251.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>2441435.2</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>2441435.2</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>2486763.3</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>2745284.78</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>2745284.78</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51870,10 @@
           <t>-239474.8400212508</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>3067251</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>3067251.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52039,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52223,11 @@
           <t>33.98999999999999</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>34.92</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>36.15</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>36.15</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52274,16 @@
           <t>746700.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>2530086.4</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>2530086.4</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>2848651.5</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>2788241.7</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>2788241.7</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52300,10 @@
           <t>-330300.2709706062</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>746700</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>746700.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52469,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52653,11 @@
           <t>34.08</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>35.03</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>35.03</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>36.21</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52704,16 @@
           <t>1628033.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>2979894.0</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>2979894</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>3115544.6</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>2857333.8</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>2857333.8</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52730,10 @@
           <t>-199623.9840778778</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>1628033</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>1628033.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
@@ -53629,7 +52899,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -53813,15 +53083,11 @@
           <t>34.17</t>
         </is>
       </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>35.12</t>
-        </is>
-      </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>36.27</t>
-        </is>
+      <c r="AM123" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>36.27</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -53868,20 +53134,16 @@
           <t>1278381.0</t>
         </is>
       </c>
-      <c r="AX123" t="inlineStr">
-        <is>
-          <t>3035213.4</t>
-        </is>
+      <c r="AX123" t="n">
+        <v>3035213.4</v>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
           <t>3208352.2</t>
         </is>
       </c>
-      <c r="AZ123" t="inlineStr">
-        <is>
-          <t>2902801.48</t>
-        </is>
+      <c r="AZ123" t="n">
+        <v>2902801.48</v>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
@@ -53898,8 +53160,10 @@
           <t>-100242.6819426282</t>
         </is>
       </c>
-      <c r="BD123" t="n">
-        <v>1278381</v>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>1278381.0</t>
+        </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
